--- a/光伏配储项目/电价数据/2026/旭升站.xlsx
+++ b/光伏配储项目/电价数据/2026/旭升站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50662</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8280700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57769</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.69184</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.57023</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.58414</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.14112</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.17985</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.15713</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.24922</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25016</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.11822</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.03608</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.02583</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.12971</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07851999999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.09904</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.24848</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.10657</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.23469</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.95177</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.44654</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.8192200000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.51184</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8864500000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.60598</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.71475</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.28112</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.7801699999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.75654</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.8304600000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6507500000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.64566</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.65577</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7253099999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7117899999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47936</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42214</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.78712</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76484</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.78792</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.63273</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79413</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5361399999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50625</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.54662</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.22053</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.23788</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.13685</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58466</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.8013899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.02091</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.15473</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.19647</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.00293</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25682</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.53362</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.50631</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.76436</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.26664</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.58643</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.59387</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.88079</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.97929</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.96323</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05494</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.03725</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.02961</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.31258</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.74861</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33348</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48248</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43331</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25837</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.26542</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.22523</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.16995</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.53479</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.51125</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.46649</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.54818</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.5240900000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.9673999999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.52138</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.04796</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>-0.02357</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.06966</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23559</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.84988</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.43685</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56985</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.0498</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.86621</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.10597</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.50626</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.52263</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.50692</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.44798</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34313</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.00192</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.46345</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.21453</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.95196</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.1859</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59897</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.7246900000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.5835900000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.18148</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.65363</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.60839</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.82552</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.83769</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.89093</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.62471</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.14338</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20303</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10744</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.18868</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.16149</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48936</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19313</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.21555</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.23947</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02697</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.03736</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29442</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25305</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.00861</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.01923</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.02783</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.03151</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.04103</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.03495</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.12023</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.00611</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.07621</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34865</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.64255</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.02633</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.08848</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.008919999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.03861</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19244</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.12934</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33665</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30856</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.26906</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16545</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15106</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22304</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.21991</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.16911</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.23719</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.25657</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47906</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7926599999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.61102</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.48127</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.76507</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.8871</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.47067</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.88493</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86903</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.26719</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.87279</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.60582</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.16383</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8405199999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.32029</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.01797</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7877799999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88207</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50781</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41873</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22583</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63948</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54298</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45237</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58635</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5816</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66184</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.09769</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.47646</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.56262</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.44184</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.42043</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.6097400000000001</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80455</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.22885</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.20396</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.20312</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.23151</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.22056</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>1.32296</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45184</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35285</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95639</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5497300000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.75686</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.26091</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.05897</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.13707</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.27816</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.80069</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.19985</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19493</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.26811</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20608</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2181</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.16019</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7503200000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.46809</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24754</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.46939</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59676</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86225</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.28448</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.10756</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70362</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79539</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64981</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58368</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49566</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.15427</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.6075</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.08417</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.80838</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.99617</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.86646</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.00357</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.30736</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.32657</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.0569</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.07175</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.23162</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.89695</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.38249</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.30815</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.87613</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.04966</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.14962</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.96373</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.76323</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.93429</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.91235</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.7567</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.04828</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.15069</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.10387</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.34295</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.05643</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.03353</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.53403</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.2424</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.39494</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32471</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42135</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.6810700000000001</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24249</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.25279</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13424</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.25712</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.12139</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.12923</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12995</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11901</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09672</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.09562999999999999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.15995</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.12494</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14055</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>-0.00711</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54235</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23568</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25253</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23919</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23563</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.24355</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22589</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26658</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.47993</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.4801</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.18158</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7074400000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95105</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.1831</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.13545</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.03271</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5455399999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.27111</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.27319</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.58335</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.02261</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.48086</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.6217999999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.08609</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.02377</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.07022</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.9504199999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.94314</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.01051</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.8119700000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.77232</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48834</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.26431</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.94277</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.97265</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.49273</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.94485</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.9693200000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.56638</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5273600000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.49286</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.08388</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.99188</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.9994500000000001</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.5321699999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.54028</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.50426</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.57456</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.03177</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.14307</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.99327</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.52664</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.59742</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.07501</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.39208</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.5501699999999999</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.58247</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.8959900000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.22959</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2932</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.7744099999999999</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.45969</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.91044</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.22344</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5638200000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42502</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8311499999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34478</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44012</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.5181</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.54947</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76447</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.77262</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.24171</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.21666</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>1.28288</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>1.33881</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>1.39474</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>1.54848</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5027900000000001</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72621</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76536</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55576</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50285</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02494</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.53633</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.45404</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.14148</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.13497</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.15596</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.7888999999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.78796</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.69296</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.8686200000000001</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.81684</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.82298</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.48011</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.50303</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.86105</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5246900000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.01393</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9652500000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44909</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45723</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.47279</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47814</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.56075</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.16498</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40881</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5603400000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.94587</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.56432</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.61061</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.56433</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.63427</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.88985</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.24448</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.7509600000000001</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.6866599999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.67671</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.16634</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.72168</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.23377</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.73105</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67073</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.57111</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.52155</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.20568</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.83439</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.59488</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.23417</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.44302</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.48932</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8487899999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.47305</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.5850700000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.57009</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.35526</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42657</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45774</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80375</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.80984</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.7726799999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.08768</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.64732</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.8598600000000001</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.72537</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.5715800000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.06537000000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22553</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51254</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.11116</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.09556000000000001</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.21612</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36414</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22378</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22074</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.21689</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.11131</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.21286</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.13411</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.24759</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.12968</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.13868</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>-0.02315</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.20988</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.12794</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.20831</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35167</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22048</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20836</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.14704</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17437</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.009269999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.02808</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11814</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.23753</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.09755</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.03039</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.01461</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03466</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.07198</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.20519</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24196</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.24681</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.25774</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26227</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25182</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25083</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26097</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24616</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.22959</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.18776</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.03531</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.03001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.22899</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.21281</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.19462</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.11754</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.25616</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25672</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.23733</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.21365</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.1968</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17915</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.20706</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.21756</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15641</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.21573</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21349</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.23653</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.20491</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.21773</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.23921</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21705</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.17285</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.46243</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.46562</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.65438</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18556</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08855</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20171</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.08563</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.02019</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.01312</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18706</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.01369</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.01466</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.11418</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.09434000000000001</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.06681999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.01505</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.07144</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.43215</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.18972</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32353</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.06179</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.68076</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.54855</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52791</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.94973</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.42097</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.27219</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.18494</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.27511</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.16536</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.16001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.1959</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.21405</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.81908</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55699</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56349</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.65822</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13322</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.11873</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.0007199999999999999</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.51386</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.48663</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32976</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.73988</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.08145</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.61085</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.20952</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.42101</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.87212</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.43821</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.83184</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.10701</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.12952</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.17711</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.22704</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.29675</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.30924</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.28723</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.34936</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.22984</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.16889</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.55006</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.48311</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.16488</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.26357</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.06755</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.8740399999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.8740800000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.91728</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.83297</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6873899999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.6388400000000001</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5294800000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.52665</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.53459</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.59224</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.58993</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.50848</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.05673</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.98277</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.45815</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.25066</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17327</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.47707</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.88446</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.03167</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.14012</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.14211</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.25001</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.16293</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.25365</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.23532</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.26732</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.26821</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.19313</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.28932</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.26978</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.29705</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.36971</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.72964</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.73329</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.5558200000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.21323</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.30384</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.33175</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.48533</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57685</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.49881</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7019500000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.68075</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.01472</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9561499999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.72336</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72515</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.42991</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37508</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8159400000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.32279</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.01045</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9404</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9667100000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.11601</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.24989</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.2401</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8708899999999999</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.71608</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.50943</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.34155</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.36223</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.16192</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8745499999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04493</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7097899999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.10543</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.9998899999999999</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.11744</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.11753</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.17763</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.1151</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5313099999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.21062</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.81974</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.65566</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.21026</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.9155800000000001</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.81592</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.19367</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.98775</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.0604</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.25271</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.34602</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.08428</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.0754</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.13598</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05688</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06747</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.16512</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.13698</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.17128</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.19053</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.96129</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.68524</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.32737</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.6512100000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6317</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.13325</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.18317</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.20093</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.1816</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.47792</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.82133</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.72636</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.65551</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.6212300000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37545</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.68588</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.32193</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31903</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.06681</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.07431</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.52152</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.7649900000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.6646599999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.84088</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.85761</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.80502</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.09595</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.9054099999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.10138</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.96929</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.75236</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.74139</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.8895</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.8685</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.65727</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.9730700000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.5972799999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.86542</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.19953</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.09494</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.23953</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.7845599999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.96376</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.47582</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.11315</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.06157</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.23789</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>-0.00959</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.46373</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.50707</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.17634</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.19981</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.19963</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.08384999999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.21081</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21694</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23552</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.05817</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.19866</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.03073</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.07463</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.13111</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.17837</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.19916</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.03256000000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52686</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.20245</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.14535</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.9779800000000001</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18511</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5535800000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18724</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.19679</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.80411</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.00906</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.17566</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.06367</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18727</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.19824</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.25401</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.25807</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36164</v>
       </c>
     </row>
   </sheetData>
